--- a/Tefas Funds/data/fon_kategorileri_kontrol.xlsx
+++ b/Tefas Funds/data/fon_kategorileri_kontrol.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\Portfolio\Tefas Funds\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD17334D-5F3D-4C25-9CB3-B8349768603B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5871A9-84C0-4F4A-A7E2-22E3ADF2EE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fon_Kategorileri" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fon_Kategorileri!$A$1:$A$851</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -5182,18 +5185,12 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -5223,12 +5220,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5531,6 +5527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C851"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5550,7 +5547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5561,7 +5558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5572,7 +5569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5583,7 +5580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -5594,7 +5591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5605,7 +5602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -5616,7 +5613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -5627,7 +5624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -5638,7 +5635,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -5649,7 +5646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -5660,7 +5657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -5671,7 +5668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -5682,7 +5679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -5693,7 +5690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -5704,7 +5701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -5715,7 +5712,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -5726,7 +5723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -5737,7 +5734,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -5748,7 +5745,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -5759,7 +5756,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -5770,7 +5767,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -5781,7 +5778,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -5792,7 +5789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -5803,7 +5800,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -5814,7 +5811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -5825,7 +5822,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -5836,7 +5833,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -5847,7 +5844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -5858,7 +5855,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -5869,7 +5866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -5880,7 +5877,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -5891,7 +5888,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -5902,7 +5899,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -5913,7 +5910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -5924,7 +5921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -5935,7 +5932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -5946,7 +5943,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -5957,7 +5954,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -5968,7 +5965,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -5979,7 +5976,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>90</v>
       </c>
@@ -5990,7 +5987,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>92</v>
       </c>
@@ -6001,7 +5998,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -6012,7 +6009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -6023,7 +6020,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -6034,7 +6031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>100</v>
       </c>
@@ -6045,7 +6042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -6056,7 +6053,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -6067,7 +6064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -6078,7 +6075,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>108</v>
       </c>
@@ -6089,7 +6086,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>110</v>
       </c>
@@ -6100,7 +6097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -6111,7 +6108,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>115</v>
       </c>
@@ -6122,7 +6119,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>117</v>
       </c>
@@ -6133,7 +6130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>119</v>
       </c>
@@ -6144,7 +6141,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>121</v>
       </c>
@@ -6155,7 +6152,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>123</v>
       </c>
@@ -6166,7 +6163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>125</v>
       </c>
@@ -6177,7 +6174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>127</v>
       </c>
@@ -6188,7 +6185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -6199,7 +6196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>131</v>
       </c>
@@ -6210,7 +6207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>133</v>
       </c>
@@ -6221,7 +6218,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>135</v>
       </c>
@@ -6232,7 +6229,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>137</v>
       </c>
@@ -6243,7 +6240,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>139</v>
       </c>
@@ -6254,7 +6251,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>141</v>
       </c>
@@ -6265,7 +6262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>143</v>
       </c>
@@ -6276,7 +6273,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>145</v>
       </c>
@@ -6287,7 +6284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>147</v>
       </c>
@@ -6298,7 +6295,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>149</v>
       </c>
@@ -6309,7 +6306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>151</v>
       </c>
@@ -6320,7 +6317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -6331,7 +6328,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>155</v>
       </c>
@@ -6342,7 +6339,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>157</v>
       </c>
@@ -6353,7 +6350,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>159</v>
       </c>
@@ -6364,7 +6361,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>161</v>
       </c>
@@ -6375,7 +6372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>163</v>
       </c>
@@ -6386,7 +6383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -6397,7 +6394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>167</v>
       </c>
@@ -6408,7 +6405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>169</v>
       </c>
@@ -6419,7 +6416,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>171</v>
       </c>
@@ -6430,7 +6427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>173</v>
       </c>
@@ -6441,7 +6438,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>175</v>
       </c>
@@ -6452,7 +6449,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>177</v>
       </c>
@@ -6463,7 +6460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>179</v>
       </c>
@@ -6474,7 +6471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>181</v>
       </c>
@@ -6485,7 +6482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>183</v>
       </c>
@@ -6496,7 +6493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>185</v>
       </c>
@@ -6507,7 +6504,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>187</v>
       </c>
@@ -6518,7 +6515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>189</v>
       </c>
@@ -6529,7 +6526,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>191</v>
       </c>
@@ -6540,7 +6537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>193</v>
       </c>
@@ -6551,7 +6548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>195</v>
       </c>
@@ -6562,7 +6559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>197</v>
       </c>
@@ -6573,7 +6570,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>199</v>
       </c>
@@ -6584,7 +6581,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>201</v>
       </c>
@@ -6595,7 +6592,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>203</v>
       </c>
@@ -6606,7 +6603,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>205</v>
       </c>
@@ -6617,7 +6614,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>207</v>
       </c>
@@ -6628,7 +6625,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>209</v>
       </c>
@@ -6639,7 +6636,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>211</v>
       </c>
@@ -6650,7 +6647,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>213</v>
       </c>
@@ -6661,7 +6658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>215</v>
       </c>
@@ -6672,7 +6669,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>217</v>
       </c>
@@ -6683,7 +6680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>219</v>
       </c>
@@ -6694,7 +6691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>221</v>
       </c>
@@ -6705,7 +6702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>223</v>
       </c>
@@ -6716,7 +6713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>225</v>
       </c>
@@ -6727,7 +6724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>227</v>
       </c>
@@ -6738,7 +6735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>229</v>
       </c>
@@ -6749,7 +6746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>231</v>
       </c>
@@ -6760,7 +6757,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>233</v>
       </c>
@@ -6771,7 +6768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>235</v>
       </c>
@@ -6782,7 +6779,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>237</v>
       </c>
@@ -6793,7 +6790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>239</v>
       </c>
@@ -6804,7 +6801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>241</v>
       </c>
@@ -6815,7 +6812,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>243</v>
       </c>
@@ -6826,7 +6823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>245</v>
       </c>
@@ -6837,7 +6834,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>247</v>
       </c>
@@ -6848,7 +6845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>249</v>
       </c>
@@ -6859,7 +6856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>251</v>
       </c>
@@ -6870,7 +6867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>253</v>
       </c>
@@ -6881,7 +6878,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>255</v>
       </c>
@@ -6892,7 +6889,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>257</v>
       </c>
@@ -6903,7 +6900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>259</v>
       </c>
@@ -6914,7 +6911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>261</v>
       </c>
@@ -6925,7 +6922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>263</v>
       </c>
@@ -6936,7 +6933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>265</v>
       </c>
@@ -6947,7 +6944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -6958,7 +6955,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>269</v>
       </c>
@@ -6969,7 +6966,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>271</v>
       </c>
@@ -6980,7 +6977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>273</v>
       </c>
@@ -6991,7 +6988,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>275</v>
       </c>
@@ -7002,7 +6999,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>277</v>
       </c>
@@ -7013,7 +7010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>279</v>
       </c>
@@ -7024,7 +7021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>281</v>
       </c>
@@ -7035,7 +7032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>283</v>
       </c>
@@ -7046,7 +7043,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>285</v>
       </c>
@@ -7057,7 +7054,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>287</v>
       </c>
@@ -7068,7 +7065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>289</v>
       </c>
@@ -7079,7 +7076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>291</v>
       </c>
@@ -7090,7 +7087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>293</v>
       </c>
@@ -7101,7 +7098,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>295</v>
       </c>
@@ -7112,7 +7109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>297</v>
       </c>
@@ -7123,7 +7120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>299</v>
       </c>
@@ -7134,7 +7131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>301</v>
       </c>
@@ -7145,7 +7142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>303</v>
       </c>
@@ -7156,7 +7153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>305</v>
       </c>
@@ -7167,7 +7164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>307</v>
       </c>
@@ -7178,7 +7175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>309</v>
       </c>
@@ -7189,7 +7186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>311</v>
       </c>
@@ -7200,7 +7197,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>313</v>
       </c>
@@ -7211,7 +7208,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>315</v>
       </c>
@@ -7222,7 +7219,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>317</v>
       </c>
@@ -7233,7 +7230,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>319</v>
       </c>
@@ -7244,7 +7241,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>321</v>
       </c>
@@ -7255,7 +7252,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>323</v>
       </c>
@@ -7266,7 +7263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>325</v>
       </c>
@@ -7277,7 +7274,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>327</v>
       </c>
@@ -7288,7 +7285,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>329</v>
       </c>
@@ -7299,7 +7296,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>331</v>
       </c>
@@ -7310,7 +7307,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>333</v>
       </c>
@@ -7321,7 +7318,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>335</v>
       </c>
@@ -7332,7 +7329,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>337</v>
       </c>
@@ -7343,7 +7340,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>339</v>
       </c>
@@ -7354,7 +7351,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>341</v>
       </c>
@@ -7365,7 +7362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>343</v>
       </c>
@@ -7376,7 +7373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>345</v>
       </c>
@@ -7387,7 +7384,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>347</v>
       </c>
@@ -7398,7 +7395,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>349</v>
       </c>
@@ -7409,7 +7406,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>351</v>
       </c>
@@ -7420,7 +7417,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>353</v>
       </c>
@@ -7431,7 +7428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>355</v>
       </c>
@@ -7442,7 +7439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>357</v>
       </c>
@@ -7453,7 +7450,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>359</v>
       </c>
@@ -7464,7 +7461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>361</v>
       </c>
@@ -7475,7 +7472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>363</v>
       </c>
@@ -7486,7 +7483,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>365</v>
       </c>
@@ -7497,7 +7494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>367</v>
       </c>
@@ -7508,7 +7505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>369</v>
       </c>
@@ -7519,7 +7516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>371</v>
       </c>
@@ -7530,7 +7527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>373</v>
       </c>
@@ -7541,7 +7538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>375</v>
       </c>
@@ -7552,7 +7549,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>377</v>
       </c>
@@ -7563,7 +7560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>379</v>
       </c>
@@ -7574,7 +7571,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>381</v>
       </c>
@@ -7585,7 +7582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>383</v>
       </c>
@@ -7596,7 +7593,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>385</v>
       </c>
@@ -7607,7 +7604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>387</v>
       </c>
@@ -7618,7 +7615,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>389</v>
       </c>
@@ -7629,7 +7626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>391</v>
       </c>
@@ -7640,7 +7637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>393</v>
       </c>
@@ -7651,7 +7648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>395</v>
       </c>
@@ -7662,7 +7659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>397</v>
       </c>
@@ -7673,7 +7670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>399</v>
       </c>
@@ -7684,7 +7681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>401</v>
       </c>
@@ -7695,7 +7692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>403</v>
       </c>
@@ -7706,7 +7703,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>405</v>
       </c>
@@ -7717,7 +7714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>407</v>
       </c>
@@ -7728,7 +7725,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>409</v>
       </c>
@@ -7739,7 +7736,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>411</v>
       </c>
@@ -7750,7 +7747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>413</v>
       </c>
@@ -7761,7 +7758,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>415</v>
       </c>
@@ -7772,7 +7769,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>417</v>
       </c>
@@ -7783,7 +7780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>419</v>
       </c>
@@ -7794,7 +7791,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>421</v>
       </c>
@@ -7805,7 +7802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>423</v>
       </c>
@@ -7816,7 +7813,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>425</v>
       </c>
@@ -7827,7 +7824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>427</v>
       </c>
@@ -7838,7 +7835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>429</v>
       </c>
@@ -7849,7 +7846,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>431</v>
       </c>
@@ -7860,7 +7857,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>433</v>
       </c>
@@ -7871,7 +7868,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>435</v>
       </c>
@@ -7882,7 +7879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>437</v>
       </c>
@@ -7893,7 +7890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>439</v>
       </c>
@@ -7904,7 +7901,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>441</v>
       </c>
@@ -7915,7 +7912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>443</v>
       </c>
@@ -7926,7 +7923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>445</v>
       </c>
@@ -7937,7 +7934,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>447</v>
       </c>
@@ -7948,7 +7945,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>449</v>
       </c>
@@ -7959,7 +7956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>451</v>
       </c>
@@ -7970,7 +7967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>453</v>
       </c>
@@ -7981,7 +7978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>455</v>
       </c>
@@ -7992,7 +7989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>457</v>
       </c>
@@ -8003,7 +8000,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>459</v>
       </c>
@@ -8014,7 +8011,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>461</v>
       </c>
@@ -8025,7 +8022,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>463</v>
       </c>
@@ -8036,7 +8033,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>465</v>
       </c>
@@ -8047,7 +8044,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>467</v>
       </c>
@@ -8058,7 +8055,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>469</v>
       </c>
@@ -8069,7 +8066,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>471</v>
       </c>
@@ -8080,7 +8077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>473</v>
       </c>
@@ -8091,7 +8088,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>475</v>
       </c>
@@ -8102,7 +8099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>477</v>
       </c>
@@ -8113,7 +8110,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>479</v>
       </c>
@@ -8124,7 +8121,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>481</v>
       </c>
@@ -8135,7 +8132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>483</v>
       </c>
@@ -8146,7 +8143,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>485</v>
       </c>
@@ -8157,7 +8154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>487</v>
       </c>
@@ -8168,18 +8165,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="2" t="s">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
         <v>489</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B240" t="s">
         <v>490</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="C240" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>491</v>
       </c>
@@ -8190,7 +8187,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>493</v>
       </c>
@@ -8201,7 +8198,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>495</v>
       </c>
@@ -8212,7 +8209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>497</v>
       </c>
@@ -8223,7 +8220,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>499</v>
       </c>
@@ -8234,7 +8231,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>501</v>
       </c>
@@ -8245,7 +8242,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>503</v>
       </c>
@@ -8256,7 +8253,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>505</v>
       </c>
@@ -8267,7 +8264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>507</v>
       </c>
@@ -8278,7 +8275,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>509</v>
       </c>
@@ -8289,7 +8286,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>511</v>
       </c>
@@ -8300,7 +8297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>513</v>
       </c>
@@ -8311,7 +8308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>515</v>
       </c>
@@ -8322,7 +8319,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>517</v>
       </c>
@@ -8333,7 +8330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>519</v>
       </c>
@@ -8344,7 +8341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>521</v>
       </c>
@@ -8355,7 +8352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>523</v>
       </c>
@@ -8366,7 +8363,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>525</v>
       </c>
@@ -8377,7 +8374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>527</v>
       </c>
@@ -8388,7 +8385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>529</v>
       </c>
@@ -8399,7 +8396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>531</v>
       </c>
@@ -8410,7 +8407,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>533</v>
       </c>
@@ -8421,7 +8418,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>535</v>
       </c>
@@ -8432,7 +8429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>537</v>
       </c>
@@ -8443,7 +8440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>539</v>
       </c>
@@ -8454,7 +8451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>541</v>
       </c>
@@ -8465,7 +8462,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>543</v>
       </c>
@@ -8476,7 +8473,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>545</v>
       </c>
@@ -8487,7 +8484,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>547</v>
       </c>
@@ -8498,7 +8495,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>549</v>
       </c>
@@ -8509,7 +8506,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>551</v>
       </c>
@@ -8520,7 +8517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>553</v>
       </c>
@@ -8531,7 +8528,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>555</v>
       </c>
@@ -8542,7 +8539,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>557</v>
       </c>
@@ -8553,7 +8550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>559</v>
       </c>
@@ -8564,7 +8561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>561</v>
       </c>
@@ -8575,7 +8572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>563</v>
       </c>
@@ -8586,7 +8583,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>565</v>
       </c>
@@ -8597,7 +8594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>567</v>
       </c>
@@ -8608,7 +8605,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>569</v>
       </c>
@@ -8619,7 +8616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>571</v>
       </c>
@@ -8630,7 +8627,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>573</v>
       </c>
@@ -8641,7 +8638,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>575</v>
       </c>
@@ -8652,7 +8649,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>577</v>
       </c>
@@ -8663,7 +8660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>579</v>
       </c>
@@ -8674,7 +8671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>581</v>
       </c>
@@ -8685,7 +8682,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>583</v>
       </c>
@@ -8696,7 +8693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>585</v>
       </c>
@@ -8707,7 +8704,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>587</v>
       </c>
@@ -8718,7 +8715,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>589</v>
       </c>
@@ -8729,7 +8726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>591</v>
       </c>
@@ -8740,7 +8737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>593</v>
       </c>
@@ -8751,7 +8748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>595</v>
       </c>
@@ -8762,7 +8759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>597</v>
       </c>
@@ -8773,7 +8770,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>599</v>
       </c>
@@ -8784,7 +8781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>601</v>
       </c>
@@ -8795,7 +8792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>603</v>
       </c>
@@ -8806,7 +8803,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>605</v>
       </c>
@@ -8817,7 +8814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>607</v>
       </c>
@@ -8828,7 +8825,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>609</v>
       </c>
@@ -8839,7 +8836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>611</v>
       </c>
@@ -8850,7 +8847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>613</v>
       </c>
@@ -8861,7 +8858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>615</v>
       </c>
@@ -8872,7 +8869,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>617</v>
       </c>
@@ -8883,7 +8880,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>619</v>
       </c>
@@ -8894,7 +8891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>621</v>
       </c>
@@ -8905,7 +8902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>623</v>
       </c>
@@ -8916,7 +8913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>625</v>
       </c>
@@ -8927,7 +8924,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>627</v>
       </c>
@@ -8938,7 +8935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>629</v>
       </c>
@@ -8949,7 +8946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>631</v>
       </c>
@@ -8960,7 +8957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>633</v>
       </c>
@@ -8971,7 +8968,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>635</v>
       </c>
@@ -8982,7 +8979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>637</v>
       </c>
@@ -8993,7 +8990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>639</v>
       </c>
@@ -9004,7 +9001,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>641</v>
       </c>
@@ -9015,7 +9012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>643</v>
       </c>
@@ -9026,7 +9023,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>645</v>
       </c>
@@ -9037,7 +9034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>647</v>
       </c>
@@ -9048,7 +9045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>649</v>
       </c>
@@ -9059,7 +9056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>651</v>
       </c>
@@ -9070,7 +9067,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>653</v>
       </c>
@@ -9081,7 +9078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>655</v>
       </c>
@@ -9092,7 +9089,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>657</v>
       </c>
@@ -9103,7 +9100,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>659</v>
       </c>
@@ -9114,7 +9111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>661</v>
       </c>
@@ -9125,7 +9122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>663</v>
       </c>
@@ -9136,7 +9133,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>665</v>
       </c>
@@ -9147,7 +9144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>667</v>
       </c>
@@ -9158,7 +9155,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>669</v>
       </c>
@@ -9169,7 +9166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>671</v>
       </c>
@@ -9180,7 +9177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>673</v>
       </c>
@@ -9191,7 +9188,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>675</v>
       </c>
@@ -9202,7 +9199,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>677</v>
       </c>
@@ -9213,7 +9210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>679</v>
       </c>
@@ -9224,7 +9221,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>681</v>
       </c>
@@ -9235,7 +9232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>683</v>
       </c>
@@ -9246,7 +9243,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>685</v>
       </c>
@@ -9257,7 +9254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>687</v>
       </c>
@@ -9268,7 +9265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>689</v>
       </c>
@@ -9279,7 +9276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>691</v>
       </c>
@@ -9290,7 +9287,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>693</v>
       </c>
@@ -9301,7 +9298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>695</v>
       </c>
@@ -9312,7 +9309,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>697</v>
       </c>
@@ -9323,7 +9320,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>699</v>
       </c>
@@ -9334,7 +9331,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>701</v>
       </c>
@@ -9345,7 +9342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>703</v>
       </c>
@@ -9356,7 +9353,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>705</v>
       </c>
@@ -9367,7 +9364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>707</v>
       </c>
@@ -9378,7 +9375,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>709</v>
       </c>
@@ -9389,7 +9386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>711</v>
       </c>
@@ -9400,7 +9397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>713</v>
       </c>
@@ -9411,7 +9408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>715</v>
       </c>
@@ -9422,7 +9419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>717</v>
       </c>
@@ -9433,7 +9430,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>719</v>
       </c>
@@ -9444,7 +9441,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>721</v>
       </c>
@@ -9455,7 +9452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>723</v>
       </c>
@@ -9466,7 +9463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>725</v>
       </c>
@@ -9477,7 +9474,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>727</v>
       </c>
@@ -9488,7 +9485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>729</v>
       </c>
@@ -9499,7 +9496,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>731</v>
       </c>
@@ -9510,7 +9507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>733</v>
       </c>
@@ -9521,7 +9518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>735</v>
       </c>
@@ -9532,7 +9529,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>737</v>
       </c>
@@ -9543,7 +9540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>739</v>
       </c>
@@ -9554,7 +9551,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>742</v>
       </c>
@@ -9565,7 +9562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>744</v>
       </c>
@@ -9576,7 +9573,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>746</v>
       </c>
@@ -9587,7 +9584,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>748</v>
       </c>
@@ -9598,7 +9595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>750</v>
       </c>
@@ -9609,7 +9606,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>752</v>
       </c>
@@ -9620,7 +9617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>754</v>
       </c>
@@ -9631,7 +9628,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>756</v>
       </c>
@@ -9642,7 +9639,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>758</v>
       </c>
@@ -9653,7 +9650,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>760</v>
       </c>
@@ -9664,7 +9661,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>762</v>
       </c>
@@ -9675,7 +9672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>764</v>
       </c>
@@ -9686,7 +9683,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>766</v>
       </c>
@@ -9697,7 +9694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>768</v>
       </c>
@@ -9708,7 +9705,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>770</v>
       </c>
@@ -9719,7 +9716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>772</v>
       </c>
@@ -9730,7 +9727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>774</v>
       </c>
@@ -9741,7 +9738,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>776</v>
       </c>
@@ -9752,7 +9749,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>778</v>
       </c>
@@ -9763,7 +9760,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>780</v>
       </c>
@@ -9774,7 +9771,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>782</v>
       </c>
@@ -9785,7 +9782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>784</v>
       </c>
@@ -9796,7 +9793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>786</v>
       </c>
@@ -9807,7 +9804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>788</v>
       </c>
@@ -9818,7 +9815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>790</v>
       </c>
@@ -9829,7 +9826,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>792</v>
       </c>
@@ -9840,7 +9837,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>794</v>
       </c>
@@ -9851,7 +9848,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>796</v>
       </c>
@@ -9862,7 +9859,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>798</v>
       </c>
@@ -9873,7 +9870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>800</v>
       </c>
@@ -9884,7 +9881,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>802</v>
       </c>
@@ -9895,7 +9892,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>804</v>
       </c>
@@ -9906,7 +9903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>806</v>
       </c>
@@ -9917,7 +9914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>808</v>
       </c>
@@ -9928,7 +9925,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>810</v>
       </c>
@@ -9939,7 +9936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>812</v>
       </c>
@@ -9950,7 +9947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>814</v>
       </c>
@@ -9961,7 +9958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>816</v>
       </c>
@@ -9972,7 +9969,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>818</v>
       </c>
@@ -9983,7 +9980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>820</v>
       </c>
@@ -9994,7 +9991,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>822</v>
       </c>
@@ -10005,7 +10002,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>824</v>
       </c>
@@ -10016,7 +10013,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>826</v>
       </c>
@@ -10027,7 +10024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>828</v>
       </c>
@@ -10038,7 +10035,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>830</v>
       </c>
@@ -10049,7 +10046,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>832</v>
       </c>
@@ -10060,7 +10057,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>834</v>
       </c>
@@ -10071,7 +10068,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>836</v>
       </c>
@@ -10082,7 +10079,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>838</v>
       </c>
@@ -10093,7 +10090,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>840</v>
       </c>
@@ -10104,7 +10101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>842</v>
       </c>
@@ -10115,7 +10112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>844</v>
       </c>
@@ -10126,7 +10123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>846</v>
       </c>
@@ -10137,7 +10134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>848</v>
       </c>
@@ -10148,7 +10145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>850</v>
       </c>
@@ -10159,7 +10156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>852</v>
       </c>
@@ -10170,7 +10167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>854</v>
       </c>
@@ -10181,7 +10178,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>856</v>
       </c>
@@ -10192,7 +10189,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>858</v>
       </c>
@@ -10203,7 +10200,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>860</v>
       </c>
@@ -10214,7 +10211,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>862</v>
       </c>
@@ -10225,7 +10222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>864</v>
       </c>
@@ -10236,7 +10233,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>866</v>
       </c>
@@ -10247,7 +10244,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>868</v>
       </c>
@@ -10258,7 +10255,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>870</v>
       </c>
@@ -10269,7 +10266,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>872</v>
       </c>
@@ -10280,7 +10277,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>874</v>
       </c>
@@ -10291,7 +10288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>876</v>
       </c>
@@ -10302,7 +10299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>878</v>
       </c>
@@ -10313,7 +10310,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>880</v>
       </c>
@@ -10324,7 +10321,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>882</v>
       </c>
@@ -10335,7 +10332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>884</v>
       </c>
@@ -10346,7 +10343,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>886</v>
       </c>
@@ -10357,7 +10354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>888</v>
       </c>
@@ -10368,7 +10365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>890</v>
       </c>
@@ -10379,7 +10376,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>892</v>
       </c>
@@ -10390,7 +10387,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>894</v>
       </c>
@@ -10401,7 +10398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>896</v>
       </c>
@@ -10412,7 +10409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>898</v>
       </c>
@@ -10423,7 +10420,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>900</v>
       </c>
@@ -10434,7 +10431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>902</v>
       </c>
@@ -10445,7 +10442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>904</v>
       </c>
@@ -10456,7 +10453,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>906</v>
       </c>
@@ -10467,7 +10464,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>908</v>
       </c>
@@ -10478,7 +10475,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>910</v>
       </c>
@@ -10489,7 +10486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>912</v>
       </c>
@@ -10500,7 +10497,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>914</v>
       </c>
@@ -10511,7 +10508,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>916</v>
       </c>
@@ -10522,7 +10519,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>918</v>
       </c>
@@ -10533,7 +10530,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>920</v>
       </c>
@@ -10544,7 +10541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>922</v>
       </c>
@@ -10555,7 +10552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>924</v>
       </c>
@@ -10566,7 +10563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>926</v>
       </c>
@@ -10577,7 +10574,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>928</v>
       </c>
@@ -10588,7 +10585,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>930</v>
       </c>
@@ -10599,7 +10596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>932</v>
       </c>
@@ -10610,7 +10607,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>934</v>
       </c>
@@ -10621,7 +10618,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>936</v>
       </c>
@@ -10632,7 +10629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>938</v>
       </c>
@@ -10643,7 +10640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>940</v>
       </c>
@@ -10654,7 +10651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>942</v>
       </c>
@@ -10665,7 +10662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>944</v>
       </c>
@@ -10676,7 +10673,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>946</v>
       </c>
@@ -10687,7 +10684,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>948</v>
       </c>
@@ -10698,7 +10695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>950</v>
       </c>
@@ -10709,7 +10706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>952</v>
       </c>
@@ -10720,7 +10717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>954</v>
       </c>
@@ -10731,7 +10728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>956</v>
       </c>
@@ -10742,7 +10739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>958</v>
       </c>
@@ -10753,7 +10750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>960</v>
       </c>
@@ -10764,7 +10761,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>962</v>
       </c>
@@ -10775,7 +10772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>964</v>
       </c>
@@ -10786,7 +10783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>966</v>
       </c>
@@ -10797,7 +10794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>968</v>
       </c>
@@ -10808,7 +10805,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>970</v>
       </c>
@@ -10819,7 +10816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>972</v>
       </c>
@@ -10830,7 +10827,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>974</v>
       </c>
@@ -10841,7 +10838,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>976</v>
       </c>
@@ -10852,7 +10849,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>978</v>
       </c>
@@ -10863,7 +10860,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>980</v>
       </c>
@@ -10874,7 +10871,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>982</v>
       </c>
@@ -10885,7 +10882,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>984</v>
       </c>
@@ -10896,7 +10893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>986</v>
       </c>
@@ -10907,7 +10904,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>988</v>
       </c>
@@ -10918,7 +10915,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>990</v>
       </c>
@@ -10929,7 +10926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>992</v>
       </c>
@@ -10940,7 +10937,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>994</v>
       </c>
@@ -10951,7 +10948,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>996</v>
       </c>
@@ -10962,7 +10959,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>998</v>
       </c>
@@ -10973,7 +10970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1000</v>
       </c>
@@ -10984,7 +10981,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1002</v>
       </c>
@@ -10995,7 +10992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1004</v>
       </c>
@@ -11006,7 +11003,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1006</v>
       </c>
@@ -11017,7 +11014,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1008</v>
       </c>
@@ -11028,7 +11025,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1010</v>
       </c>
@@ -11039,7 +11036,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1012</v>
       </c>
@@ -11050,7 +11047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>1014</v>
       </c>
@@ -11061,7 +11058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1016</v>
       </c>
@@ -11072,7 +11069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1018</v>
       </c>
@@ -11083,7 +11080,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>1020</v>
       </c>
@@ -11094,7 +11091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1022</v>
       </c>
@@ -11105,7 +11102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>1024</v>
       </c>
@@ -11116,7 +11113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>1026</v>
       </c>
@@ -11127,7 +11124,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>1028</v>
       </c>
@@ -11138,7 +11135,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1030</v>
       </c>
@@ -11149,7 +11146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>1032</v>
       </c>
@@ -11160,7 +11157,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>1034</v>
       </c>
@@ -11171,7 +11168,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>1036</v>
       </c>
@@ -11182,7 +11179,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>1038</v>
       </c>
@@ -11193,7 +11190,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>1040</v>
       </c>
@@ -11204,7 +11201,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>1042</v>
       </c>
@@ -11215,7 +11212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>1044</v>
       </c>
@@ -11226,7 +11223,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1046</v>
       </c>
@@ -11237,7 +11234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>1048</v>
       </c>
@@ -11248,7 +11245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1050</v>
       </c>
@@ -11259,7 +11256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>1052</v>
       </c>
@@ -11270,7 +11267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>1054</v>
       </c>
@@ -11281,7 +11278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>1056</v>
       </c>
@@ -11292,7 +11289,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>1058</v>
       </c>
@@ -11303,7 +11300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>1060</v>
       </c>
@@ -11314,7 +11311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>1062</v>
       </c>
@@ -11325,7 +11322,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1064</v>
       </c>
@@ -11336,7 +11333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>1066</v>
       </c>
@@ -11347,7 +11344,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>1068</v>
       </c>
@@ -11358,7 +11355,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1070</v>
       </c>
@@ -11369,7 +11366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>1072</v>
       </c>
@@ -11380,7 +11377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>1074</v>
       </c>
@@ -11391,7 +11388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>1076</v>
       </c>
@@ -11402,7 +11399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>1078</v>
       </c>
@@ -11413,7 +11410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>1080</v>
       </c>
@@ -11424,7 +11421,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>1082</v>
       </c>
@@ -11435,7 +11432,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>1084</v>
       </c>
@@ -11446,7 +11443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>1086</v>
       </c>
@@ -11457,7 +11454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>1088</v>
       </c>
@@ -11468,7 +11465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>1090</v>
       </c>
@@ -11479,7 +11476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>1092</v>
       </c>
@@ -11490,7 +11487,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>1094</v>
       </c>
@@ -11501,7 +11498,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1096</v>
       </c>
@@ -11512,7 +11509,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>1098</v>
       </c>
@@ -11523,7 +11520,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>1100</v>
       </c>
@@ -11534,7 +11531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1102</v>
       </c>
@@ -11545,7 +11542,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>1104</v>
       </c>
@@ -11556,7 +11553,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>1106</v>
       </c>
@@ -11567,7 +11564,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>1108</v>
       </c>
@@ -11578,7 +11575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>1110</v>
       </c>
@@ -11589,7 +11586,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>1112</v>
       </c>
@@ -11600,7 +11597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>1114</v>
       </c>
@@ -11611,7 +11608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>1116</v>
       </c>
@@ -11622,7 +11619,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>1118</v>
       </c>
@@ -11633,7 +11630,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>1120</v>
       </c>
@@ -11644,7 +11641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>1122</v>
       </c>
@@ -11655,7 +11652,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>1124</v>
       </c>
@@ -11666,7 +11663,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>1126</v>
       </c>
@@ -11677,7 +11674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>1128</v>
       </c>
@@ -11688,7 +11685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>1130</v>
       </c>
@@ -11699,7 +11696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>1132</v>
       </c>
@@ -11710,7 +11707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>1134</v>
       </c>
@@ -11721,7 +11718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>1136</v>
       </c>
@@ -11732,7 +11729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>1138</v>
       </c>
@@ -11743,7 +11740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>1140</v>
       </c>
@@ -11754,7 +11751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>1142</v>
       </c>
@@ -11765,7 +11762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>1144</v>
       </c>
@@ -11776,7 +11773,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>1146</v>
       </c>
@@ -11787,7 +11784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>1148</v>
       </c>
@@ -11798,7 +11795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>1150</v>
       </c>
@@ -11809,7 +11806,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>1152</v>
       </c>
@@ -11820,7 +11817,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>1154</v>
       </c>
@@ -11831,7 +11828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>1156</v>
       </c>
@@ -11842,7 +11839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>1158</v>
       </c>
@@ -11853,7 +11850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>1160</v>
       </c>
@@ -11864,7 +11861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>1162</v>
       </c>
@@ -11875,7 +11872,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>1164</v>
       </c>
@@ -11886,7 +11883,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>1166</v>
       </c>
@@ -11897,7 +11894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>1168</v>
       </c>
@@ -11908,7 +11905,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>1170</v>
       </c>
@@ -11919,7 +11916,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>1172</v>
       </c>
@@ -11930,7 +11927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>1174</v>
       </c>
@@ -11941,7 +11938,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>1176</v>
       </c>
@@ -11952,7 +11949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>1178</v>
       </c>
@@ -11963,7 +11960,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>1180</v>
       </c>
@@ -11974,7 +11971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>1182</v>
       </c>
@@ -11985,7 +11982,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>1184</v>
       </c>
@@ -11996,7 +11993,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>1186</v>
       </c>
@@ -12007,7 +12004,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>1188</v>
       </c>
@@ -12018,7 +12015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>1190</v>
       </c>
@@ -12029,7 +12026,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>1192</v>
       </c>
@@ -12040,7 +12037,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>1194</v>
       </c>
@@ -12051,7 +12048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>1196</v>
       </c>
@@ -12062,7 +12059,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>1198</v>
       </c>
@@ -12073,7 +12070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>1200</v>
       </c>
@@ -12084,7 +12081,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>1202</v>
       </c>
@@ -12095,7 +12092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>1204</v>
       </c>
@@ -12106,7 +12103,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>1206</v>
       </c>
@@ -12117,7 +12114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>1208</v>
       </c>
@@ -12128,7 +12125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>1210</v>
       </c>
@@ -12139,7 +12136,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>1212</v>
       </c>
@@ -12150,7 +12147,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>1214</v>
       </c>
@@ -12161,7 +12158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>1216</v>
       </c>
@@ -12172,7 +12169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>1218</v>
       </c>
@@ -12183,7 +12180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>1220</v>
       </c>
@@ -12194,7 +12191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>1222</v>
       </c>
@@ -12205,7 +12202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>1224</v>
       </c>
@@ -12216,7 +12213,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>1226</v>
       </c>
@@ -12227,7 +12224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>1228</v>
       </c>
@@ -12238,7 +12235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>1230</v>
       </c>
@@ -12249,7 +12246,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>1232</v>
       </c>
@@ -12260,7 +12257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>1234</v>
       </c>
@@ -12271,7 +12268,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>1236</v>
       </c>
@@ -12282,7 +12279,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>1238</v>
       </c>
@@ -12293,7 +12290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>1240</v>
       </c>
@@ -12304,7 +12301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>1242</v>
       </c>
@@ -12315,7 +12312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>1244</v>
       </c>
@@ -12326,7 +12323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>1246</v>
       </c>
@@ -12337,7 +12334,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>1248</v>
       </c>
@@ -12348,7 +12345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>1250</v>
       </c>
@@ -12359,7 +12356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>1252</v>
       </c>
@@ -12370,7 +12367,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>1254</v>
       </c>
@@ -12381,7 +12378,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>1256</v>
       </c>
@@ -12392,7 +12389,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>1258</v>
       </c>
@@ -12403,7 +12400,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>1260</v>
       </c>
@@ -12414,7 +12411,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>1262</v>
       </c>
@@ -12425,7 +12422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>1264</v>
       </c>
@@ -12436,7 +12433,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>1266</v>
       </c>
@@ -12447,7 +12444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>1268</v>
       </c>
@@ -12458,7 +12455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>1270</v>
       </c>
@@ -12469,7 +12466,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>1272</v>
       </c>
@@ -12480,7 +12477,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>1274</v>
       </c>
@@ -12491,7 +12488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>1276</v>
       </c>
@@ -12502,7 +12499,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>1278</v>
       </c>
@@ -12513,7 +12510,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>1280</v>
       </c>
@@ -12524,7 +12521,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>1282</v>
       </c>
@@ -12535,7 +12532,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>1284</v>
       </c>
@@ -12546,7 +12543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>1286</v>
       </c>
@@ -12557,7 +12554,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>1288</v>
       </c>
@@ -12568,7 +12565,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>1290</v>
       </c>
@@ -12579,7 +12576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>1292</v>
       </c>
@@ -12590,7 +12587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>1294</v>
       </c>
@@ -12601,7 +12598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>1296</v>
       </c>
@@ -12612,7 +12609,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>1298</v>
       </c>
@@ -12623,7 +12620,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>1300</v>
       </c>
@@ -12634,7 +12631,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>1302</v>
       </c>
@@ -12645,7 +12642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>1304</v>
       </c>
@@ -12656,7 +12653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>1306</v>
       </c>
@@ -12667,7 +12664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>1308</v>
       </c>
@@ -12678,7 +12675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>1310</v>
       </c>
@@ -12689,7 +12686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>1312</v>
       </c>
@@ -12700,7 +12697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>1314</v>
       </c>
@@ -12711,7 +12708,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>1316</v>
       </c>
@@ -12722,7 +12719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>1318</v>
       </c>
@@ -12733,7 +12730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>1320</v>
       </c>
@@ -12744,7 +12741,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>1322</v>
       </c>
@@ -12755,7 +12752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>1324</v>
       </c>
@@ -12766,7 +12763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>1326</v>
       </c>
@@ -12777,7 +12774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>1328</v>
       </c>
@@ -12788,7 +12785,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>1330</v>
       </c>
@@ -12799,7 +12796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>1332</v>
       </c>
@@ -12810,7 +12807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>1334</v>
       </c>
@@ -12821,7 +12818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>1336</v>
       </c>
@@ -12832,7 +12829,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>1338</v>
       </c>
@@ -12843,7 +12840,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>1340</v>
       </c>
@@ -12854,7 +12851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>1342</v>
       </c>
@@ -12865,7 +12862,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>1344</v>
       </c>
@@ -12876,7 +12873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>1346</v>
       </c>
@@ -12887,7 +12884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>1348</v>
       </c>
@@ -12898,7 +12895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>1350</v>
       </c>
@@ -12909,7 +12906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>1352</v>
       </c>
@@ -12920,7 +12917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>1354</v>
       </c>
@@ -12931,7 +12928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>1356</v>
       </c>
@@ -12942,7 +12939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>1358</v>
       </c>
@@ -12953,7 +12950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>1360</v>
       </c>
@@ -12964,7 +12961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>1362</v>
       </c>
@@ -12975,7 +12972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>1364</v>
       </c>
@@ -12986,7 +12983,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>1366</v>
       </c>
@@ -12997,7 +12994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>1368</v>
       </c>
@@ -13008,7 +13005,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>1370</v>
       </c>
@@ -13019,7 +13016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>1372</v>
       </c>
@@ -13030,7 +13027,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>1374</v>
       </c>
@@ -13041,7 +13038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>1376</v>
       </c>
@@ -13052,7 +13049,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>1378</v>
       </c>
@@ -13063,7 +13060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>1380</v>
       </c>
@@ -13074,7 +13071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>1382</v>
       </c>
@@ -13085,7 +13082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>1384</v>
       </c>
@@ -13096,7 +13093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>1386</v>
       </c>
@@ -13107,7 +13104,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>1388</v>
       </c>
@@ -13118,7 +13115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>1390</v>
       </c>
@@ -13129,7 +13126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>1392</v>
       </c>
@@ -13140,7 +13137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>1394</v>
       </c>
@@ -13151,7 +13148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>1396</v>
       </c>
@@ -13162,7 +13159,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>1398</v>
       </c>
@@ -13173,7 +13170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>1400</v>
       </c>
@@ -13184,7 +13181,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>1402</v>
       </c>
@@ -13195,7 +13192,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>1404</v>
       </c>
@@ -13206,7 +13203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>1406</v>
       </c>
@@ -13217,7 +13214,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>1408</v>
       </c>
@@ -13228,7 +13225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>1410</v>
       </c>
@@ -13239,7 +13236,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>1412</v>
       </c>
@@ -13250,7 +13247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>1414</v>
       </c>
@@ -13261,7 +13258,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>1416</v>
       </c>
@@ -13272,7 +13269,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>1418</v>
       </c>
@@ -13283,7 +13280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>1420</v>
       </c>
@@ -13294,7 +13291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>1422</v>
       </c>
@@ -13305,18 +13302,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A707" s="2" t="s">
+    <row r="707" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
         <v>1424</v>
       </c>
-      <c r="B707" s="2" t="s">
+      <c r="B707" t="s">
         <v>1425</v>
       </c>
-      <c r="C707" s="2" t="s">
+      <c r="C707" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>1426</v>
       </c>
@@ -13327,7 +13324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>1428</v>
       </c>
@@ -13338,7 +13335,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>1430</v>
       </c>
@@ -13349,7 +13346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>1432</v>
       </c>
@@ -13360,7 +13357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>1434</v>
       </c>
@@ -13371,7 +13368,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>1436</v>
       </c>
@@ -13382,7 +13379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>1438</v>
       </c>
@@ -13393,7 +13390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>1440</v>
       </c>
@@ -13404,7 +13401,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>1442</v>
       </c>
@@ -13415,7 +13412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>1444</v>
       </c>
@@ -13426,7 +13423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>1446</v>
       </c>
@@ -13437,7 +13434,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>1448</v>
       </c>
@@ -13448,7 +13445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>1450</v>
       </c>
@@ -13459,7 +13456,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>1452</v>
       </c>
@@ -13470,7 +13467,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>1454</v>
       </c>
@@ -13481,7 +13478,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>1456</v>
       </c>
@@ -13492,7 +13489,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>1458</v>
       </c>
@@ -13514,7 +13511,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>1462</v>
       </c>
@@ -13525,7 +13522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>1464</v>
       </c>
@@ -13536,7 +13533,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>1466</v>
       </c>
@@ -13547,7 +13544,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>1468</v>
       </c>
@@ -13558,7 +13555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>1470</v>
       </c>
@@ -13569,7 +13566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>1472</v>
       </c>
@@ -13580,7 +13577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>1474</v>
       </c>
@@ -13591,7 +13588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>1476</v>
       </c>
@@ -13602,7 +13599,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>1478</v>
       </c>
@@ -13613,7 +13610,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>1480</v>
       </c>
@@ -13624,7 +13621,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>1482</v>
       </c>
@@ -13635,7 +13632,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>1484</v>
       </c>
@@ -13646,7 +13643,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>1486</v>
       </c>
@@ -13657,7 +13654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>1488</v>
       </c>
@@ -13668,7 +13665,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>1490</v>
       </c>
@@ -13679,7 +13676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>1492</v>
       </c>
@@ -13690,7 +13687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>1494</v>
       </c>
@@ -13701,7 +13698,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>1496</v>
       </c>
@@ -13712,7 +13709,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>1498</v>
       </c>
@@ -13723,7 +13720,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>1500</v>
       </c>
@@ -13734,7 +13731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>1502</v>
       </c>
@@ -13745,7 +13742,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>1504</v>
       </c>
@@ -13756,7 +13753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>1506</v>
       </c>
@@ -13767,7 +13764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>1508</v>
       </c>
@@ -13778,7 +13775,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>1510</v>
       </c>
@@ -13789,7 +13786,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>1512</v>
       </c>
@@ -13800,7 +13797,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>1514</v>
       </c>
@@ -13811,7 +13808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>1516</v>
       </c>
@@ -13822,7 +13819,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>1518</v>
       </c>
@@ -13833,7 +13830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>1520</v>
       </c>
@@ -13844,7 +13841,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>1522</v>
       </c>
@@ -13855,7 +13852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>1524</v>
       </c>
@@ -13866,7 +13863,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>1526</v>
       </c>
@@ -13877,7 +13874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>1528</v>
       </c>
@@ -13888,7 +13885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>1530</v>
       </c>
@@ -13899,7 +13896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>1532</v>
       </c>
@@ -13910,7 +13907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>1534</v>
       </c>
@@ -13921,7 +13918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>1536</v>
       </c>
@@ -13932,7 +13929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>1538</v>
       </c>
@@ -13943,7 +13940,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>1540</v>
       </c>
@@ -13954,7 +13951,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>1542</v>
       </c>
@@ -13965,7 +13962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>1544</v>
       </c>
@@ -13976,18 +13973,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="768" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A768" s="2" t="s">
+    <row r="768" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A768" t="s">
         <v>1546</v>
       </c>
-      <c r="B768" s="2" t="s">
+      <c r="B768" t="s">
         <v>1547</v>
       </c>
-      <c r="C768" s="2" t="s">
+      <c r="C768" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>1548</v>
       </c>
@@ -13998,7 +13995,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>1550</v>
       </c>
@@ -14009,7 +14006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>1552</v>
       </c>
@@ -14020,7 +14017,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>1554</v>
       </c>
@@ -14031,7 +14028,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>1556</v>
       </c>
@@ -14042,7 +14039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>1558</v>
       </c>
@@ -14053,7 +14050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>1560</v>
       </c>
@@ -14064,7 +14061,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>1562</v>
       </c>
@@ -14075,7 +14072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>1564</v>
       </c>
@@ -14086,7 +14083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>1566</v>
       </c>
@@ -14097,7 +14094,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>1568</v>
       </c>
@@ -14108,7 +14105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>1570</v>
       </c>
@@ -14119,7 +14116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>1572</v>
       </c>
@@ -14130,7 +14127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>1574</v>
       </c>
@@ -14141,7 +14138,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>1576</v>
       </c>
@@ -14152,7 +14149,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>1578</v>
       </c>
@@ -14163,7 +14160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>1580</v>
       </c>
@@ -14174,7 +14171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>1582</v>
       </c>
@@ -14185,7 +14182,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>1584</v>
       </c>
@@ -14196,7 +14193,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>1586</v>
       </c>
@@ -14207,7 +14204,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>1588</v>
       </c>
@@ -14218,7 +14215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>1590</v>
       </c>
@@ -14229,7 +14226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>1592</v>
       </c>
@@ -14240,7 +14237,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>1594</v>
       </c>
@@ -14251,7 +14248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>1596</v>
       </c>
@@ -14262,7 +14259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>1598</v>
       </c>
@@ -14273,7 +14270,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>1600</v>
       </c>
@@ -14284,7 +14281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>1602</v>
       </c>
@@ -14295,7 +14292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>1604</v>
       </c>
@@ -14306,7 +14303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>1606</v>
       </c>
@@ -14317,7 +14314,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>1608</v>
       </c>
@@ -14328,7 +14325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>1610</v>
       </c>
@@ -14339,7 +14336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>1612</v>
       </c>
@@ -14350,7 +14347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>1614</v>
       </c>
@@ -14361,7 +14358,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>1616</v>
       </c>
@@ -14372,7 +14369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>1618</v>
       </c>
@@ -14383,7 +14380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>1620</v>
       </c>
@@ -14394,7 +14391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>1622</v>
       </c>
@@ -14405,7 +14402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>1624</v>
       </c>
@@ -14416,7 +14413,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>1626</v>
       </c>
@@ -14427,7 +14424,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>1628</v>
       </c>
@@ -14438,7 +14435,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>1630</v>
       </c>
@@ -14449,7 +14446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>1632</v>
       </c>
@@ -14460,7 +14457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>1634</v>
       </c>
@@ -14471,7 +14468,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>1636</v>
       </c>
@@ -14482,7 +14479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>1638</v>
       </c>
@@ -14493,7 +14490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>1640</v>
       </c>
@@ -14504,7 +14501,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>1642</v>
       </c>
@@ -14515,7 +14512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>1644</v>
       </c>
@@ -14526,7 +14523,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>1646</v>
       </c>
@@ -14537,7 +14534,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>1648</v>
       </c>
@@ -14548,7 +14545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>1650</v>
       </c>
@@ -14559,7 +14556,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>1652</v>
       </c>
@@ -14570,7 +14567,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>1654</v>
       </c>
@@ -14581,7 +14578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>1656</v>
       </c>
@@ -14592,7 +14589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>1658</v>
       </c>
@@ -14603,7 +14600,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>1660</v>
       </c>
@@ -14614,7 +14611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>1662</v>
       </c>
@@ -14625,7 +14622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>1664</v>
       </c>
@@ -14636,7 +14633,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="828" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>1666</v>
       </c>
@@ -14647,7 +14644,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="829" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>1668</v>
       </c>
@@ -14658,7 +14655,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="830" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>1670</v>
       </c>
@@ -14669,7 +14666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="831" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>1672</v>
       </c>
@@ -14680,7 +14677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="832" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>1674</v>
       </c>
@@ -14691,7 +14688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="833" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>1676</v>
       </c>
@@ -14702,7 +14699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="834" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>1678</v>
       </c>
@@ -14713,7 +14710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="835" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>1680</v>
       </c>
@@ -14724,7 +14721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="836" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>1682</v>
       </c>
@@ -14735,7 +14732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="837" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>1684</v>
       </c>
@@ -14746,7 +14743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="838" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>1686</v>
       </c>
@@ -14757,7 +14754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="839" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>1688</v>
       </c>
@@ -14768,7 +14765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="840" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>1690</v>
       </c>
@@ -14779,7 +14776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="841" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>1692</v>
       </c>
@@ -14790,7 +14787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="842" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>1694</v>
       </c>
@@ -14801,7 +14798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="843" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>1696</v>
       </c>
@@ -14812,7 +14809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="844" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>1698</v>
       </c>
@@ -14823,7 +14820,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="845" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>1700</v>
       </c>
@@ -14834,7 +14831,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="846" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>1702</v>
       </c>
@@ -14845,7 +14842,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="847" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>1704</v>
       </c>
@@ -14856,7 +14853,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>1706</v>
       </c>
@@ -14867,7 +14864,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="849" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>1708</v>
       </c>
@@ -14878,7 +14875,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="850" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>1710</v>
       </c>
@@ -14889,7 +14886,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="851" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>1712</v>
       </c>
@@ -14901,6 +14898,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A851" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="TLE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Tefas Funds/data/fon_kategorileri_kontrol.xlsx
+++ b/Tefas Funds/data/fon_kategorileri_kontrol.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\Portfolio\Tefas Funds\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A8F719-4C3D-4130-9937-312A8C1AE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5C2843-28B5-4219-BC5D-C33C2003BDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fon_Kategorileri" sheetId="1" r:id="rId1"/>
@@ -5527,6 +5527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C851"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5546,7 +5547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5557,7 +5558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5568,7 +5569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5579,7 +5580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -5590,7 +5591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5601,7 +5602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -5612,7 +5613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -5623,7 +5624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -5634,7 +5635,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -5645,7 +5646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -5656,7 +5657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -5667,7 +5668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -5678,7 +5679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -5689,7 +5690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -5700,7 +5701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -5711,7 +5712,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -5722,7 +5723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -5733,7 +5734,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -5744,7 +5745,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -5755,7 +5756,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -5766,7 +5767,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -5777,7 +5778,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -5788,7 +5789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -5799,7 +5800,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -5810,7 +5811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -5821,7 +5822,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -5832,7 +5833,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -5843,7 +5844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -5854,7 +5855,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -5865,7 +5866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -5876,7 +5877,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -5887,7 +5888,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -5898,7 +5899,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -5909,7 +5910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -5920,7 +5921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -5931,7 +5932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -5942,7 +5943,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -5953,7 +5954,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -5975,7 +5976,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>90</v>
       </c>
@@ -5986,7 +5987,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>92</v>
       </c>
@@ -5997,7 +5998,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -6008,7 +6009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -6019,7 +6020,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -6030,7 +6031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>100</v>
       </c>
@@ -6041,7 +6042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -6052,7 +6053,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -6063,7 +6064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -6074,7 +6075,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>108</v>
       </c>
@@ -6085,7 +6086,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>110</v>
       </c>
@@ -6096,7 +6097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -6107,7 +6108,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>115</v>
       </c>
@@ -6118,7 +6119,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>117</v>
       </c>
@@ -6129,7 +6130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>119</v>
       </c>
@@ -6140,7 +6141,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>121</v>
       </c>
@@ -6151,7 +6152,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>123</v>
       </c>
@@ -6162,7 +6163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>125</v>
       </c>
@@ -6173,7 +6174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>127</v>
       </c>
@@ -6184,7 +6185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -6195,7 +6196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>131</v>
       </c>
@@ -6206,7 +6207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>133</v>
       </c>
@@ -6217,7 +6218,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>135</v>
       </c>
@@ -6228,7 +6229,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>137</v>
       </c>
@@ -6239,7 +6240,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>139</v>
       </c>
@@ -6250,7 +6251,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>141</v>
       </c>
@@ -6261,7 +6262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>143</v>
       </c>
@@ -6272,7 +6273,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>145</v>
       </c>
@@ -6283,7 +6284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>147</v>
       </c>
@@ -6294,7 +6295,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>149</v>
       </c>
@@ -6305,7 +6306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>151</v>
       </c>
@@ -6316,7 +6317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -6327,7 +6328,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>155</v>
       </c>
@@ -6338,7 +6339,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>157</v>
       </c>
@@ -6349,7 +6350,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>159</v>
       </c>
@@ -6360,7 +6361,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>161</v>
       </c>
@@ -6371,7 +6372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>163</v>
       </c>
@@ -6382,7 +6383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -6393,7 +6394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>167</v>
       </c>
@@ -6404,7 +6405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>169</v>
       </c>
@@ -6415,7 +6416,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>171</v>
       </c>
@@ -6426,7 +6427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>173</v>
       </c>
@@ -6437,7 +6438,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>175</v>
       </c>
@@ -6448,7 +6449,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>177</v>
       </c>
@@ -6459,7 +6460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>179</v>
       </c>
@@ -6470,7 +6471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>181</v>
       </c>
@@ -6481,7 +6482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>183</v>
       </c>
@@ -6492,7 +6493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>185</v>
       </c>
@@ -6503,7 +6504,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>187</v>
       </c>
@@ -6514,7 +6515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>189</v>
       </c>
@@ -6525,7 +6526,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>191</v>
       </c>
@@ -6536,7 +6537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>193</v>
       </c>
@@ -6547,7 +6548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>195</v>
       </c>
@@ -6558,7 +6559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>197</v>
       </c>
@@ -6569,7 +6570,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>199</v>
       </c>
@@ -6580,7 +6581,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>201</v>
       </c>
@@ -6591,7 +6592,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>203</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>205</v>
       </c>
@@ -6613,7 +6614,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>207</v>
       </c>
@@ -6624,7 +6625,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>209</v>
       </c>
@@ -6635,7 +6636,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>211</v>
       </c>
@@ -6646,7 +6647,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>213</v>
       </c>
@@ -6657,7 +6658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>215</v>
       </c>
@@ -6668,7 +6669,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>217</v>
       </c>
@@ -6679,7 +6680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>219</v>
       </c>
@@ -6690,7 +6691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>221</v>
       </c>
@@ -6701,7 +6702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>223</v>
       </c>
@@ -6712,7 +6713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>225</v>
       </c>
@@ -6723,7 +6724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>227</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>229</v>
       </c>
@@ -6745,7 +6746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>231</v>
       </c>
@@ -6756,7 +6757,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>233</v>
       </c>
@@ -6767,7 +6768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>235</v>
       </c>
@@ -6778,7 +6779,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>237</v>
       </c>
@@ -6789,7 +6790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>239</v>
       </c>
@@ -6800,7 +6801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>241</v>
       </c>
@@ -6811,7 +6812,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>243</v>
       </c>
@@ -6822,7 +6823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>245</v>
       </c>
@@ -6833,7 +6834,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>247</v>
       </c>
@@ -6844,7 +6845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>249</v>
       </c>
@@ -6855,7 +6856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>251</v>
       </c>
@@ -6866,7 +6867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>253</v>
       </c>
@@ -6877,7 +6878,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>255</v>
       </c>
@@ -6888,7 +6889,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>257</v>
       </c>
@@ -6899,7 +6900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>259</v>
       </c>
@@ -6910,7 +6911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>261</v>
       </c>
@@ -6921,7 +6922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>263</v>
       </c>
@@ -6932,7 +6933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>265</v>
       </c>
@@ -6943,7 +6944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -6954,7 +6955,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>269</v>
       </c>
@@ -6965,7 +6966,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>271</v>
       </c>
@@ -6976,7 +6977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>273</v>
       </c>
@@ -6987,7 +6988,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>275</v>
       </c>
@@ -6998,7 +6999,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>277</v>
       </c>
@@ -7009,7 +7010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>279</v>
       </c>
@@ -7020,7 +7021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>281</v>
       </c>
@@ -7031,7 +7032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>283</v>
       </c>
@@ -7042,7 +7043,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>285</v>
       </c>
@@ -7053,7 +7054,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>287</v>
       </c>
@@ -7064,7 +7065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>289</v>
       </c>
@@ -7075,7 +7076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>291</v>
       </c>
@@ -7086,7 +7087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>293</v>
       </c>
@@ -7097,7 +7098,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>295</v>
       </c>
@@ -7108,7 +7109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>297</v>
       </c>
@@ -7119,7 +7120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>299</v>
       </c>
@@ -7130,7 +7131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>301</v>
       </c>
@@ -7141,7 +7142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>303</v>
       </c>
@@ -7152,7 +7153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>305</v>
       </c>
@@ -7163,7 +7164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>307</v>
       </c>
@@ -7174,7 +7175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>309</v>
       </c>
@@ -7185,7 +7186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>311</v>
       </c>
@@ -7196,7 +7197,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>313</v>
       </c>
@@ -7207,7 +7208,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>315</v>
       </c>
@@ -7218,7 +7219,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>317</v>
       </c>
@@ -7229,7 +7230,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>319</v>
       </c>
@@ -7240,7 +7241,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>321</v>
       </c>
@@ -7251,7 +7252,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>323</v>
       </c>
@@ -7262,7 +7263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>325</v>
       </c>
@@ -7273,7 +7274,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>327</v>
       </c>
@@ -7284,7 +7285,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>329</v>
       </c>
@@ -7295,7 +7296,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>331</v>
       </c>
@@ -7306,7 +7307,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>333</v>
       </c>
@@ -7317,7 +7318,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>335</v>
       </c>
@@ -7328,7 +7329,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>337</v>
       </c>
@@ -7339,7 +7340,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>339</v>
       </c>
@@ -7350,7 +7351,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>341</v>
       </c>
@@ -7361,7 +7362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>343</v>
       </c>
@@ -7372,7 +7373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>345</v>
       </c>
@@ -7383,7 +7384,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>347</v>
       </c>
@@ -7394,7 +7395,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>349</v>
       </c>
@@ -7405,7 +7406,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>351</v>
       </c>
@@ -7416,7 +7417,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>353</v>
       </c>
@@ -7427,7 +7428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>355</v>
       </c>
@@ -7438,7 +7439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>357</v>
       </c>
@@ -7449,7 +7450,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>359</v>
       </c>
@@ -7460,7 +7461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>361</v>
       </c>
@@ -7471,7 +7472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>363</v>
       </c>
@@ -7482,7 +7483,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>365</v>
       </c>
@@ -7493,7 +7494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>367</v>
       </c>
@@ -7504,7 +7505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>369</v>
       </c>
@@ -7515,7 +7516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>371</v>
       </c>
@@ -7526,7 +7527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>373</v>
       </c>
@@ -7537,7 +7538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>375</v>
       </c>
@@ -7548,7 +7549,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>377</v>
       </c>
@@ -7559,7 +7560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>379</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>381</v>
       </c>
@@ -7581,7 +7582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>383</v>
       </c>
@@ -7592,7 +7593,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>385</v>
       </c>
@@ -7603,7 +7604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>387</v>
       </c>
@@ -7614,7 +7615,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>389</v>
       </c>
@@ -7625,7 +7626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>391</v>
       </c>
@@ -7636,7 +7637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>393</v>
       </c>
@@ -7647,7 +7648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>395</v>
       </c>
@@ -7658,7 +7659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>397</v>
       </c>
@@ -7669,7 +7670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>399</v>
       </c>
@@ -7680,7 +7681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>401</v>
       </c>
@@ -7691,7 +7692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>403</v>
       </c>
@@ -7702,7 +7703,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>405</v>
       </c>
@@ -7713,7 +7714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>407</v>
       </c>
@@ -7724,7 +7725,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>409</v>
       </c>
@@ -7735,7 +7736,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>411</v>
       </c>
@@ -7746,7 +7747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>413</v>
       </c>
@@ -7757,7 +7758,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>415</v>
       </c>
@@ -7768,7 +7769,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>417</v>
       </c>
@@ -7779,7 +7780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>419</v>
       </c>
@@ -7790,7 +7791,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>421</v>
       </c>
@@ -7801,7 +7802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>423</v>
       </c>
@@ -7812,7 +7813,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>425</v>
       </c>
@@ -7823,7 +7824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>427</v>
       </c>
@@ -7834,7 +7835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>429</v>
       </c>
@@ -7845,7 +7846,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>431</v>
       </c>
@@ -7856,7 +7857,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>433</v>
       </c>
@@ -7867,7 +7868,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>435</v>
       </c>
@@ -7878,7 +7879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>437</v>
       </c>
@@ -7889,7 +7890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>439</v>
       </c>
@@ -7900,7 +7901,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>441</v>
       </c>
@@ -7911,7 +7912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>443</v>
       </c>
@@ -7922,7 +7923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>445</v>
       </c>
@@ -7933,7 +7934,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>447</v>
       </c>
@@ -7944,7 +7945,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>449</v>
       </c>
@@ -7955,7 +7956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>451</v>
       </c>
@@ -7966,7 +7967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>453</v>
       </c>
@@ -7977,7 +7978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>455</v>
       </c>
@@ -7988,7 +7989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>457</v>
       </c>
@@ -7999,7 +8000,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>459</v>
       </c>
@@ -8010,7 +8011,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>461</v>
       </c>
@@ -8021,7 +8022,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>463</v>
       </c>
@@ -8032,7 +8033,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>465</v>
       </c>
@@ -8043,7 +8044,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>467</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>469</v>
       </c>
@@ -8065,7 +8066,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>471</v>
       </c>
@@ -8076,7 +8077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>473</v>
       </c>
@@ -8087,7 +8088,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>475</v>
       </c>
@@ -8098,7 +8099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>477</v>
       </c>
@@ -8109,7 +8110,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>479</v>
       </c>
@@ -8120,7 +8121,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>481</v>
       </c>
@@ -8131,7 +8132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>483</v>
       </c>
@@ -8142,7 +8143,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>485</v>
       </c>
@@ -8153,7 +8154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>487</v>
       </c>
@@ -8164,7 +8165,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>489</v>
       </c>
@@ -8175,7 +8176,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>491</v>
       </c>
@@ -8186,7 +8187,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>493</v>
       </c>
@@ -8197,7 +8198,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>495</v>
       </c>
@@ -8208,7 +8209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>497</v>
       </c>
@@ -8219,7 +8220,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>499</v>
       </c>
@@ -8230,7 +8231,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>501</v>
       </c>
@@ -8241,7 +8242,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>503</v>
       </c>
@@ -8252,7 +8253,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>505</v>
       </c>
@@ -8263,7 +8264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>507</v>
       </c>
@@ -8274,7 +8275,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>509</v>
       </c>
@@ -8285,7 +8286,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>511</v>
       </c>
@@ -8296,7 +8297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>513</v>
       </c>
@@ -8307,7 +8308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>515</v>
       </c>
@@ -8318,7 +8319,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>517</v>
       </c>
@@ -8329,7 +8330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>519</v>
       </c>
@@ -8340,7 +8341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>521</v>
       </c>
@@ -8351,7 +8352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>523</v>
       </c>
@@ -8362,7 +8363,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>525</v>
       </c>
@@ -8373,7 +8374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>527</v>
       </c>
@@ -8384,7 +8385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>529</v>
       </c>
@@ -8395,7 +8396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>531</v>
       </c>
@@ -8406,7 +8407,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>533</v>
       </c>
@@ -8417,7 +8418,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>535</v>
       </c>
@@ -8428,7 +8429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>537</v>
       </c>
@@ -8439,7 +8440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>539</v>
       </c>
@@ -8450,7 +8451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>541</v>
       </c>
@@ -8461,7 +8462,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>543</v>
       </c>
@@ -8472,7 +8473,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>545</v>
       </c>
@@ -8483,7 +8484,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>547</v>
       </c>
@@ -8494,7 +8495,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>549</v>
       </c>
@@ -8505,7 +8506,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>551</v>
       </c>
@@ -8516,7 +8517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>553</v>
       </c>
@@ -8527,7 +8528,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>555</v>
       </c>
@@ -8538,7 +8539,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>557</v>
       </c>
@@ -8549,7 +8550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>559</v>
       </c>
@@ -8560,7 +8561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>561</v>
       </c>
@@ -8571,7 +8572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>563</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>565</v>
       </c>
@@ -8593,7 +8594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>567</v>
       </c>
@@ -8604,7 +8605,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>569</v>
       </c>
@@ -8615,7 +8616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>571</v>
       </c>
@@ -8626,7 +8627,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>573</v>
       </c>
@@ -8637,7 +8638,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>575</v>
       </c>
@@ -8648,7 +8649,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>577</v>
       </c>
@@ -8659,7 +8660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>579</v>
       </c>
@@ -8670,7 +8671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>581</v>
       </c>
@@ -8681,7 +8682,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>583</v>
       </c>
@@ -8692,7 +8693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>585</v>
       </c>
@@ -8703,7 +8704,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>587</v>
       </c>
@@ -8714,7 +8715,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>589</v>
       </c>
@@ -8725,7 +8726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>591</v>
       </c>
@@ -8736,7 +8737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>593</v>
       </c>
@@ -8747,7 +8748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>595</v>
       </c>
@@ -8758,7 +8759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>597</v>
       </c>
@@ -8769,7 +8770,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>599</v>
       </c>
@@ -8780,7 +8781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>601</v>
       </c>
@@ -8791,7 +8792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>603</v>
       </c>
@@ -8802,7 +8803,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>605</v>
       </c>
@@ -8813,7 +8814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>607</v>
       </c>
@@ -8824,7 +8825,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>609</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>611</v>
       </c>
@@ -8846,7 +8847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>613</v>
       </c>
@@ -8857,7 +8858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>615</v>
       </c>
@@ -8868,7 +8869,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>617</v>
       </c>
@@ -8879,7 +8880,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>619</v>
       </c>
@@ -8890,7 +8891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>621</v>
       </c>
@@ -8901,7 +8902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>623</v>
       </c>
@@ -8912,7 +8913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>625</v>
       </c>
@@ -8923,7 +8924,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>627</v>
       </c>
@@ -8934,7 +8935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>629</v>
       </c>
@@ -8945,7 +8946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>631</v>
       </c>
@@ -8956,7 +8957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>633</v>
       </c>
@@ -8967,7 +8968,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>635</v>
       </c>
@@ -8978,7 +8979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>637</v>
       </c>
@@ -8989,7 +8990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>639</v>
       </c>
@@ -9000,7 +9001,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>641</v>
       </c>
@@ -9011,7 +9012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>643</v>
       </c>
@@ -9022,7 +9023,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>645</v>
       </c>
@@ -9033,7 +9034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>647</v>
       </c>
@@ -9044,7 +9045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>649</v>
       </c>
@@ -9055,7 +9056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>651</v>
       </c>
@@ -9066,7 +9067,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>653</v>
       </c>
@@ -9077,7 +9078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>655</v>
       </c>
@@ -9088,7 +9089,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>657</v>
       </c>
@@ -9099,7 +9100,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>659</v>
       </c>
@@ -9110,7 +9111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>661</v>
       </c>
@@ -9121,7 +9122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>663</v>
       </c>
@@ -9132,7 +9133,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>665</v>
       </c>
@@ -9143,7 +9144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>667</v>
       </c>
@@ -9154,7 +9155,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>669</v>
       </c>
@@ -9165,7 +9166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>671</v>
       </c>
@@ -9176,7 +9177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>673</v>
       </c>
@@ -9187,7 +9188,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>675</v>
       </c>
@@ -9198,7 +9199,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>677</v>
       </c>
@@ -9209,7 +9210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>679</v>
       </c>
@@ -9220,7 +9221,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>681</v>
       </c>
@@ -9231,7 +9232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>683</v>
       </c>
@@ -9242,7 +9243,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>685</v>
       </c>
@@ -9253,7 +9254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>687</v>
       </c>
@@ -9264,7 +9265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>689</v>
       </c>
@@ -9275,7 +9276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>691</v>
       </c>
@@ -9286,7 +9287,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>693</v>
       </c>
@@ -9297,7 +9298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>695</v>
       </c>
@@ -9308,7 +9309,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>697</v>
       </c>
@@ -9319,7 +9320,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>699</v>
       </c>
@@ -9330,7 +9331,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>701</v>
       </c>
@@ -9341,7 +9342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>703</v>
       </c>
@@ -9352,7 +9353,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>705</v>
       </c>
@@ -9363,7 +9364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>707</v>
       </c>
@@ -9374,7 +9375,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>709</v>
       </c>
@@ -9385,7 +9386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>711</v>
       </c>
@@ -9396,7 +9397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>713</v>
       </c>
@@ -9407,7 +9408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>715</v>
       </c>
@@ -9418,7 +9419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>717</v>
       </c>
@@ -9429,7 +9430,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>719</v>
       </c>
@@ -9440,7 +9441,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>721</v>
       </c>
@@ -9451,7 +9452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>723</v>
       </c>
@@ -9462,7 +9463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>725</v>
       </c>
@@ -9473,7 +9474,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>727</v>
       </c>
@@ -9484,7 +9485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>729</v>
       </c>
@@ -9495,7 +9496,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>731</v>
       </c>
@@ -9506,7 +9507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>733</v>
       </c>
@@ -9517,7 +9518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>735</v>
       </c>
@@ -9528,7 +9529,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>737</v>
       </c>
@@ -9550,7 +9551,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>742</v>
       </c>
@@ -9561,7 +9562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>744</v>
       </c>
@@ -9583,7 +9584,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>748</v>
       </c>
@@ -9594,7 +9595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>750</v>
       </c>
@@ -9605,7 +9606,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>752</v>
       </c>
@@ -9638,7 +9639,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>758</v>
       </c>
@@ -9649,7 +9650,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>760</v>
       </c>
@@ -9660,7 +9661,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>762</v>
       </c>
@@ -9671,7 +9672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>764</v>
       </c>
@@ -9682,7 +9683,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>766</v>
       </c>
@@ -9693,7 +9694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>768</v>
       </c>
@@ -9704,7 +9705,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>770</v>
       </c>
@@ -9715,7 +9716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>772</v>
       </c>
@@ -9726,7 +9727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>774</v>
       </c>
@@ -9748,7 +9749,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>778</v>
       </c>
@@ -9759,7 +9760,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>780</v>
       </c>
@@ -9770,7 +9771,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>782</v>
       </c>
@@ -9781,7 +9782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>784</v>
       </c>
@@ -9792,7 +9793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>786</v>
       </c>
@@ -9803,7 +9804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>788</v>
       </c>
@@ -9814,7 +9815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>790</v>
       </c>
@@ -9836,7 +9837,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>794</v>
       </c>
@@ -9847,7 +9848,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>796</v>
       </c>
@@ -9858,7 +9859,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>798</v>
       </c>
@@ -9869,7 +9870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>800</v>
       </c>
@@ -9880,7 +9881,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>802</v>
       </c>
@@ -9891,7 +9892,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>804</v>
       </c>
@@ -9902,7 +9903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>806</v>
       </c>
@@ -9913,7 +9914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>808</v>
       </c>
@@ -9924,7 +9925,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>810</v>
       </c>
@@ -9935,7 +9936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>812</v>
       </c>
@@ -9946,7 +9947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>814</v>
       </c>
@@ -9957,7 +9958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>816</v>
       </c>
@@ -9968,7 +9969,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>818</v>
       </c>
@@ -9979,7 +9980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>820</v>
       </c>
@@ -9990,7 +9991,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>822</v>
       </c>
@@ -10001,7 +10002,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>824</v>
       </c>
@@ -10012,7 +10013,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>826</v>
       </c>
@@ -10023,7 +10024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>828</v>
       </c>
@@ -10034,7 +10035,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>830</v>
       </c>
@@ -10045,7 +10046,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>832</v>
       </c>
@@ -10056,7 +10057,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>834</v>
       </c>
@@ -10067,7 +10068,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>836</v>
       </c>
@@ -10078,7 +10079,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>838</v>
       </c>
@@ -10089,7 +10090,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>840</v>
       </c>
@@ -10100,7 +10101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>842</v>
       </c>
@@ -10111,7 +10112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>844</v>
       </c>
@@ -10122,7 +10123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>846</v>
       </c>
@@ -10133,7 +10134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>848</v>
       </c>
@@ -10144,7 +10145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>850</v>
       </c>
@@ -10155,7 +10156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>852</v>
       </c>
@@ -10166,7 +10167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>854</v>
       </c>
@@ -10177,7 +10178,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>856</v>
       </c>
@@ -10188,7 +10189,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>858</v>
       </c>
@@ -10199,7 +10200,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>860</v>
       </c>
@@ -10210,7 +10211,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>862</v>
       </c>
@@ -10221,7 +10222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>864</v>
       </c>
@@ -10232,7 +10233,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>866</v>
       </c>
@@ -10243,7 +10244,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>868</v>
       </c>
@@ -10254,7 +10255,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>870</v>
       </c>
@@ -10265,7 +10266,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>872</v>
       </c>
@@ -10276,7 +10277,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>874</v>
       </c>
@@ -10287,7 +10288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>876</v>
       </c>
@@ -10298,7 +10299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>878</v>
       </c>
@@ -10309,7 +10310,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>880</v>
       </c>
@@ -10320,7 +10321,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>882</v>
       </c>
@@ -10331,7 +10332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>884</v>
       </c>
@@ -10342,7 +10343,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>886</v>
       </c>
@@ -10353,7 +10354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>888</v>
       </c>
@@ -10364,7 +10365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>890</v>
       </c>
@@ -10375,7 +10376,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>892</v>
       </c>
@@ -10386,7 +10387,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>894</v>
       </c>
@@ -10397,7 +10398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>896</v>
       </c>
@@ -10408,7 +10409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>898</v>
       </c>
@@ -10419,7 +10420,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>900</v>
       </c>
@@ -10430,7 +10431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>902</v>
       </c>
@@ -10441,7 +10442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>904</v>
       </c>
@@ -10452,7 +10453,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>906</v>
       </c>
@@ -10463,7 +10464,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>908</v>
       </c>
@@ -10474,7 +10475,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>910</v>
       </c>
@@ -10485,7 +10486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>912</v>
       </c>
@@ -10496,7 +10497,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>914</v>
       </c>
@@ -10507,7 +10508,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>916</v>
       </c>
@@ -10518,7 +10519,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>918</v>
       </c>
@@ -10529,7 +10530,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>920</v>
       </c>
@@ -10540,7 +10541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>922</v>
       </c>
@@ -10551,7 +10552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>924</v>
       </c>
@@ -10562,7 +10563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>926</v>
       </c>
@@ -10573,7 +10574,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>928</v>
       </c>
@@ -10584,7 +10585,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>930</v>
       </c>
@@ -10595,7 +10596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>932</v>
       </c>
@@ -10606,7 +10607,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>934</v>
       </c>
@@ -10617,7 +10618,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>936</v>
       </c>
@@ -10628,7 +10629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>938</v>
       </c>
@@ -10639,7 +10640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>940</v>
       </c>
@@ -10650,7 +10651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>942</v>
       </c>
@@ -10661,7 +10662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>944</v>
       </c>
@@ -10672,7 +10673,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>946</v>
       </c>
@@ -10683,7 +10684,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>948</v>
       </c>
@@ -10694,7 +10695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>950</v>
       </c>
@@ -10705,7 +10706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>952</v>
       </c>
@@ -10716,7 +10717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>954</v>
       </c>
@@ -10727,7 +10728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>956</v>
       </c>
@@ -10738,7 +10739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>958</v>
       </c>
@@ -10749,7 +10750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>960</v>
       </c>
@@ -10760,7 +10761,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>962</v>
       </c>
@@ -10771,7 +10772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>964</v>
       </c>
@@ -10782,7 +10783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>966</v>
       </c>
@@ -10793,7 +10794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>968</v>
       </c>
@@ -10804,7 +10805,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>970</v>
       </c>
@@ -10815,7 +10816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>972</v>
       </c>
@@ -10826,7 +10827,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>974</v>
       </c>
@@ -10837,7 +10838,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>976</v>
       </c>
@@ -10848,7 +10849,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>978</v>
       </c>
@@ -10859,7 +10860,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>980</v>
       </c>
@@ -10870,7 +10871,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>982</v>
       </c>
@@ -10881,7 +10882,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>984</v>
       </c>
@@ -10892,7 +10893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>986</v>
       </c>
@@ -10903,7 +10904,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>988</v>
       </c>
@@ -10914,7 +10915,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>990</v>
       </c>
@@ -10925,7 +10926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>992</v>
       </c>
@@ -10936,7 +10937,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>994</v>
       </c>
@@ -10947,7 +10948,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>996</v>
       </c>
@@ -10958,7 +10959,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>998</v>
       </c>
@@ -10969,7 +10970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1000</v>
       </c>
@@ -10980,7 +10981,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1002</v>
       </c>
@@ -10991,7 +10992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1004</v>
       </c>
@@ -11002,7 +11003,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1006</v>
       </c>
@@ -11013,7 +11014,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1008</v>
       </c>
@@ -11024,7 +11025,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1010</v>
       </c>
@@ -11035,7 +11036,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1012</v>
       </c>
@@ -11046,7 +11047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>1014</v>
       </c>
@@ -11057,7 +11058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1016</v>
       </c>
@@ -11068,7 +11069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1018</v>
       </c>
@@ -11079,7 +11080,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>1020</v>
       </c>
@@ -11090,7 +11091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1022</v>
       </c>
@@ -11101,7 +11102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>1024</v>
       </c>
@@ -11112,7 +11113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>1026</v>
       </c>
@@ -11123,7 +11124,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>1028</v>
       </c>
@@ -11134,7 +11135,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1030</v>
       </c>
@@ -11145,7 +11146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>1032</v>
       </c>
@@ -11156,7 +11157,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>1034</v>
       </c>
@@ -11167,7 +11168,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>1036</v>
       </c>
@@ -11178,7 +11179,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>1038</v>
       </c>
@@ -11189,7 +11190,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>1040</v>
       </c>
@@ -11200,7 +11201,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>1042</v>
       </c>
@@ -11211,7 +11212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>1044</v>
       </c>
@@ -11222,7 +11223,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1046</v>
       </c>
@@ -11233,7 +11234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>1048</v>
       </c>
@@ -11244,7 +11245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1050</v>
       </c>
@@ -11255,7 +11256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>1052</v>
       </c>
@@ -11266,7 +11267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>1054</v>
       </c>
@@ -11277,7 +11278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>1056</v>
       </c>
@@ -11288,7 +11289,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>1058</v>
       </c>
@@ -11299,7 +11300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>1060</v>
       </c>
@@ -11310,7 +11311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>1062</v>
       </c>
@@ -11321,7 +11322,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1064</v>
       </c>
@@ -11332,7 +11333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>1066</v>
       </c>
@@ -11343,7 +11344,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>1068</v>
       </c>
@@ -11354,7 +11355,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1070</v>
       </c>
@@ -11365,7 +11366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>1072</v>
       </c>
@@ -11376,7 +11377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>1074</v>
       </c>
@@ -11387,7 +11388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>1076</v>
       </c>
@@ -11398,7 +11399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>1078</v>
       </c>
@@ -11409,7 +11410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>1080</v>
       </c>
@@ -11420,7 +11421,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>1082</v>
       </c>
@@ -11431,7 +11432,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>1084</v>
       </c>
@@ -11442,7 +11443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>1086</v>
       </c>
@@ -11453,7 +11454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>1088</v>
       </c>
@@ -11464,7 +11465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>1090</v>
       </c>
@@ -11475,7 +11476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>1092</v>
       </c>
@@ -11486,7 +11487,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>1094</v>
       </c>
@@ -11497,7 +11498,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1096</v>
       </c>
@@ -11508,7 +11509,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>1098</v>
       </c>
@@ -11519,7 +11520,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>1100</v>
       </c>
@@ -11530,7 +11531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1102</v>
       </c>
@@ -11541,7 +11542,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>1104</v>
       </c>
@@ -11552,7 +11553,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>1106</v>
       </c>
@@ -11563,7 +11564,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>1108</v>
       </c>
@@ -11574,7 +11575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>1110</v>
       </c>
@@ -11585,7 +11586,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>1112</v>
       </c>
@@ -11596,7 +11597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>1114</v>
       </c>
@@ -11607,7 +11608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>1116</v>
       </c>
@@ -11618,7 +11619,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>1118</v>
       </c>
@@ -11629,7 +11630,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>1120</v>
       </c>
@@ -11640,7 +11641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>1122</v>
       </c>
@@ -11651,7 +11652,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>1124</v>
       </c>
@@ -11662,7 +11663,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>1126</v>
       </c>
@@ -11673,7 +11674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>1128</v>
       </c>
@@ -11684,7 +11685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>1130</v>
       </c>
@@ -11695,7 +11696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>1132</v>
       </c>
@@ -11706,7 +11707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>1134</v>
       </c>
@@ -11717,7 +11718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>1136</v>
       </c>
@@ -11728,7 +11729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>1138</v>
       </c>
@@ -11739,7 +11740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>1140</v>
       </c>
@@ -11750,7 +11751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>1142</v>
       </c>
@@ -11761,7 +11762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>1144</v>
       </c>
@@ -11772,7 +11773,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>1146</v>
       </c>
@@ -11783,7 +11784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>1148</v>
       </c>
@@ -11794,7 +11795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>1150</v>
       </c>
@@ -11805,7 +11806,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>1152</v>
       </c>
@@ -11816,7 +11817,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>1154</v>
       </c>
@@ -11827,7 +11828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>1156</v>
       </c>
@@ -11838,7 +11839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>1158</v>
       </c>
@@ -11849,7 +11850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>1160</v>
       </c>
@@ -11860,7 +11861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>1162</v>
       </c>
@@ -11871,7 +11872,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>1164</v>
       </c>
@@ -11882,7 +11883,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>1166</v>
       </c>
@@ -11893,7 +11894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>1168</v>
       </c>
@@ -11904,7 +11905,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>1170</v>
       </c>
@@ -11915,7 +11916,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>1172</v>
       </c>
@@ -11926,7 +11927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>1174</v>
       </c>
@@ -11937,7 +11938,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>1176</v>
       </c>
@@ -11948,7 +11949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>1178</v>
       </c>
@@ -11959,7 +11960,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>1180</v>
       </c>
@@ -11970,7 +11971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>1182</v>
       </c>
@@ -11981,7 +11982,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>1184</v>
       </c>
@@ -11992,7 +11993,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>1186</v>
       </c>
@@ -12003,7 +12004,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>1188</v>
       </c>
@@ -12014,7 +12015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>1190</v>
       </c>
@@ -12025,7 +12026,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>1192</v>
       </c>
@@ -12036,7 +12037,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>1194</v>
       </c>
@@ -12047,7 +12048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>1196</v>
       </c>
@@ -12058,7 +12059,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>1198</v>
       </c>
@@ -12069,7 +12070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>1200</v>
       </c>
@@ -12080,7 +12081,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>1202</v>
       </c>
@@ -12091,7 +12092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>1204</v>
       </c>
@@ -12102,7 +12103,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>1206</v>
       </c>
@@ -12113,7 +12114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>1208</v>
       </c>
@@ -12124,7 +12125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>1210</v>
       </c>
@@ -12135,7 +12136,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>1212</v>
       </c>
@@ -12146,7 +12147,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>1214</v>
       </c>
@@ -12157,7 +12158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>1216</v>
       </c>
@@ -12168,7 +12169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>1218</v>
       </c>
@@ -12179,7 +12180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>1220</v>
       </c>
@@ -12190,7 +12191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>1222</v>
       </c>
@@ -12201,7 +12202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>1224</v>
       </c>
@@ -12212,7 +12213,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>1226</v>
       </c>
@@ -12223,7 +12224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>1228</v>
       </c>
@@ -12234,7 +12235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>1230</v>
       </c>
@@ -12245,7 +12246,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>1232</v>
       </c>
@@ -12256,7 +12257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>1234</v>
       </c>
@@ -12267,7 +12268,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>1236</v>
       </c>
@@ -12278,7 +12279,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>1238</v>
       </c>
@@ -12289,7 +12290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>1240</v>
       </c>
@@ -12300,7 +12301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>1242</v>
       </c>
@@ -12311,7 +12312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>1244</v>
       </c>
@@ -12322,7 +12323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>1246</v>
       </c>
@@ -12333,7 +12334,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>1248</v>
       </c>
@@ -12344,7 +12345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>1250</v>
       </c>
@@ -12355,7 +12356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>1252</v>
       </c>
@@ -12366,7 +12367,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>1254</v>
       </c>
@@ -12377,7 +12378,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>1256</v>
       </c>
@@ -12388,7 +12389,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>1258</v>
       </c>
@@ -12399,7 +12400,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>1260</v>
       </c>
@@ -12410,7 +12411,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>1262</v>
       </c>
@@ -12421,7 +12422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>1264</v>
       </c>
@@ -12432,7 +12433,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>1266</v>
       </c>
@@ -12443,7 +12444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>1268</v>
       </c>
@@ -12454,7 +12455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>1270</v>
       </c>
@@ -12465,7 +12466,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>1272</v>
       </c>
@@ -12476,7 +12477,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>1274</v>
       </c>
@@ -12487,7 +12488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>1276</v>
       </c>
@@ -12498,7 +12499,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>1278</v>
       </c>
@@ -12509,7 +12510,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>1280</v>
       </c>
@@ -12520,7 +12521,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>1282</v>
       </c>
@@ -12531,7 +12532,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>1284</v>
       </c>
@@ -12542,7 +12543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>1286</v>
       </c>
@@ -12553,7 +12554,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>1288</v>
       </c>
@@ -12564,7 +12565,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>1290</v>
       </c>
@@ -12575,7 +12576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>1292</v>
       </c>
@@ -12586,7 +12587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>1294</v>
       </c>
@@ -12597,7 +12598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>1296</v>
       </c>
@@ -12608,7 +12609,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>1298</v>
       </c>
@@ -12619,7 +12620,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>1300</v>
       </c>
@@ -12630,7 +12631,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>1302</v>
       </c>
@@ -12641,7 +12642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>1304</v>
       </c>
@@ -12652,7 +12653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>1306</v>
       </c>
@@ -12663,7 +12664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>1308</v>
       </c>
@@ -12674,7 +12675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>1310</v>
       </c>
@@ -12685,7 +12686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>1312</v>
       </c>
@@ -12696,7 +12697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>1314</v>
       </c>
@@ -12707,7 +12708,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>1316</v>
       </c>
@@ -12718,7 +12719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>1318</v>
       </c>
@@ -12729,7 +12730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>1320</v>
       </c>
@@ -12740,7 +12741,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>1322</v>
       </c>
@@ -12751,7 +12752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>1324</v>
       </c>
@@ -12762,7 +12763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>1326</v>
       </c>
@@ -12773,7 +12774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>1328</v>
       </c>
@@ -12784,7 +12785,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>1330</v>
       </c>
@@ -12795,7 +12796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>1332</v>
       </c>
@@ -12806,7 +12807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>1334</v>
       </c>
@@ -12817,7 +12818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>1336</v>
       </c>
@@ -12828,7 +12829,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>1338</v>
       </c>
@@ -12839,7 +12840,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>1340</v>
       </c>
@@ -12850,7 +12851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>1342</v>
       </c>
@@ -12861,7 +12862,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>1344</v>
       </c>
@@ -12872,7 +12873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>1346</v>
       </c>
@@ -12883,7 +12884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>1348</v>
       </c>
@@ -12894,7 +12895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>1350</v>
       </c>
@@ -12905,7 +12906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>1352</v>
       </c>
@@ -12916,7 +12917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>1354</v>
       </c>
@@ -12927,7 +12928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>1356</v>
       </c>
@@ -12938,7 +12939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>1358</v>
       </c>
@@ -12949,7 +12950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>1360</v>
       </c>
@@ -12960,7 +12961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>1362</v>
       </c>
@@ -12971,7 +12972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>1364</v>
       </c>
@@ -12982,7 +12983,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>1366</v>
       </c>
@@ -12993,7 +12994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>1368</v>
       </c>
@@ -13004,7 +13005,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>1370</v>
       </c>
@@ -13015,7 +13016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>1372</v>
       </c>
@@ -13026,7 +13027,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>1374</v>
       </c>
@@ -13037,7 +13038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>1376</v>
       </c>
@@ -13048,7 +13049,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>1378</v>
       </c>
@@ -13059,7 +13060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>1380</v>
       </c>
@@ -13070,7 +13071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>1382</v>
       </c>
@@ -13081,7 +13082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>1384</v>
       </c>
@@ -13092,7 +13093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>1386</v>
       </c>
@@ -13103,7 +13104,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>1388</v>
       </c>
@@ -13114,7 +13115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>1390</v>
       </c>
@@ -13125,7 +13126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>1392</v>
       </c>
@@ -13136,7 +13137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>1394</v>
       </c>
@@ -13147,7 +13148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>1396</v>
       </c>
@@ -13158,7 +13159,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>1398</v>
       </c>
@@ -13169,7 +13170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>1400</v>
       </c>
@@ -13180,7 +13181,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>1402</v>
       </c>
@@ -13191,7 +13192,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>1404</v>
       </c>
@@ -13202,7 +13203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>1406</v>
       </c>
@@ -13213,7 +13214,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>1408</v>
       </c>
@@ -13224,7 +13225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>1410</v>
       </c>
@@ -13235,7 +13236,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>1412</v>
       </c>
@@ -13246,7 +13247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>1414</v>
       </c>
@@ -13257,7 +13258,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>1416</v>
       </c>
@@ -13268,7 +13269,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>1418</v>
       </c>
@@ -13279,7 +13280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>1420</v>
       </c>
@@ -13290,7 +13291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>1422</v>
       </c>
@@ -13301,7 +13302,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>1424</v>
       </c>
@@ -13312,7 +13313,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>1426</v>
       </c>
@@ -13323,7 +13324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>1428</v>
       </c>
@@ -13334,7 +13335,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>1430</v>
       </c>
@@ -13345,7 +13346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>1432</v>
       </c>
@@ -13356,7 +13357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>1434</v>
       </c>
@@ -13367,7 +13368,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>1436</v>
       </c>
@@ -13378,7 +13379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>1438</v>
       </c>
@@ -13389,7 +13390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>1440</v>
       </c>
@@ -13400,7 +13401,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>1442</v>
       </c>
@@ -13411,7 +13412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>1444</v>
       </c>
@@ -13422,7 +13423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>1446</v>
       </c>
@@ -13433,7 +13434,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>1448</v>
       </c>
@@ -13444,7 +13445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>1450</v>
       </c>
@@ -13455,7 +13456,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>1452</v>
       </c>
@@ -13466,7 +13467,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>1454</v>
       </c>
@@ -13477,7 +13478,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>1456</v>
       </c>
@@ -13488,7 +13489,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>1458</v>
       </c>
@@ -13499,7 +13500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>1460</v>
       </c>
@@ -13510,7 +13511,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>1462</v>
       </c>
@@ -13521,7 +13522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>1464</v>
       </c>
@@ -13532,7 +13533,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>1466</v>
       </c>
@@ -13543,7 +13544,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>1468</v>
       </c>
@@ -13554,7 +13555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>1470</v>
       </c>
@@ -13565,7 +13566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>1472</v>
       </c>
@@ -13576,7 +13577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>1474</v>
       </c>
@@ -13587,7 +13588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>1476</v>
       </c>
@@ -13598,7 +13599,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>1478</v>
       </c>
@@ -13609,7 +13610,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>1480</v>
       </c>
@@ -13620,7 +13621,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>1482</v>
       </c>
@@ -13631,7 +13632,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>1484</v>
       </c>
@@ -13642,7 +13643,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>1486</v>
       </c>
@@ -13653,7 +13654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>1488</v>
       </c>
@@ -13664,7 +13665,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>1490</v>
       </c>
@@ -13675,7 +13676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>1492</v>
       </c>
@@ -13686,7 +13687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>1494</v>
       </c>
@@ -13697,7 +13698,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>1496</v>
       </c>
@@ -13708,7 +13709,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>1498</v>
       </c>
@@ -13719,7 +13720,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>1500</v>
       </c>
@@ -13730,7 +13731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>1502</v>
       </c>
@@ -13741,7 +13742,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>1504</v>
       </c>
@@ -13752,7 +13753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>1506</v>
       </c>
@@ -13763,7 +13764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>1508</v>
       </c>
@@ -13774,7 +13775,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>1510</v>
       </c>
@@ -13785,7 +13786,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>1512</v>
       </c>
@@ -13796,7 +13797,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>1514</v>
       </c>
@@ -13807,7 +13808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>1516</v>
       </c>
@@ -13818,7 +13819,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>1518</v>
       </c>
@@ -13829,7 +13830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>1520</v>
       </c>
@@ -13840,7 +13841,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>1522</v>
       </c>
@@ -13851,7 +13852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>1524</v>
       </c>
@@ -13862,7 +13863,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>1526</v>
       </c>
@@ -13873,7 +13874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>1528</v>
       </c>
@@ -13884,7 +13885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>1530</v>
       </c>
@@ -13895,7 +13896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>1532</v>
       </c>
@@ -13906,7 +13907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>1534</v>
       </c>
@@ -13917,7 +13918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>1536</v>
       </c>
@@ -13928,7 +13929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>1538</v>
       </c>
@@ -13939,7 +13940,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>1540</v>
       </c>
@@ -13950,7 +13951,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>1542</v>
       </c>
@@ -13961,7 +13962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>1544</v>
       </c>
@@ -13983,7 +13984,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>1548</v>
       </c>
@@ -13994,7 +13995,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>1550</v>
       </c>
@@ -14005,7 +14006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>1552</v>
       </c>
@@ -14016,7 +14017,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>1554</v>
       </c>
@@ -14027,7 +14028,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>1556</v>
       </c>
@@ -14038,7 +14039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>1558</v>
       </c>
@@ -14049,7 +14050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>1560</v>
       </c>
@@ -14060,7 +14061,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>1562</v>
       </c>
@@ -14071,7 +14072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>1564</v>
       </c>
@@ -14082,7 +14083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>1566</v>
       </c>
@@ -14093,7 +14094,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>1568</v>
       </c>
@@ -14104,7 +14105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>1570</v>
       </c>
@@ -14115,7 +14116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>1572</v>
       </c>
@@ -14126,7 +14127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>1574</v>
       </c>
@@ -14137,7 +14138,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>1576</v>
       </c>
@@ -14148,7 +14149,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>1578</v>
       </c>
@@ -14159,7 +14160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>1580</v>
       </c>
@@ -14170,7 +14171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>1582</v>
       </c>
@@ -14181,7 +14182,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>1584</v>
       </c>
@@ -14192,7 +14193,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>1586</v>
       </c>
@@ -14203,7 +14204,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>1588</v>
       </c>
@@ -14214,7 +14215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>1590</v>
       </c>
@@ -14225,7 +14226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>1592</v>
       </c>
@@ -14236,7 +14237,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>1594</v>
       </c>
@@ -14247,7 +14248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>1596</v>
       </c>
@@ -14258,7 +14259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>1598</v>
       </c>
@@ -14269,7 +14270,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>1600</v>
       </c>
@@ -14280,7 +14281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>1602</v>
       </c>
@@ -14291,7 +14292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>1604</v>
       </c>
@@ -14302,7 +14303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>1606</v>
       </c>
@@ -14313,7 +14314,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>1608</v>
       </c>
@@ -14324,7 +14325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>1610</v>
       </c>
@@ -14335,7 +14336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>1612</v>
       </c>
@@ -14346,7 +14347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>1614</v>
       </c>
@@ -14357,7 +14358,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>1616</v>
       </c>
@@ -14368,7 +14369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>1618</v>
       </c>
@@ -14379,7 +14380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>1620</v>
       </c>
@@ -14390,7 +14391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>1622</v>
       </c>
@@ -14401,7 +14402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>1624</v>
       </c>
@@ -14412,7 +14413,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>1626</v>
       </c>
@@ -14423,7 +14424,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>1628</v>
       </c>
@@ -14434,7 +14435,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>1630</v>
       </c>
@@ -14445,7 +14446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>1632</v>
       </c>
@@ -14456,7 +14457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>1634</v>
       </c>
@@ -14467,7 +14468,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>1636</v>
       </c>
@@ -14478,7 +14479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>1638</v>
       </c>
@@ -14489,7 +14490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>1640</v>
       </c>
@@ -14500,7 +14501,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>1642</v>
       </c>
@@ -14511,7 +14512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>1644</v>
       </c>
@@ -14522,7 +14523,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>1646</v>
       </c>
@@ -14533,7 +14534,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>1648</v>
       </c>
@@ -14544,7 +14545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>1650</v>
       </c>
@@ -14555,7 +14556,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>1652</v>
       </c>
@@ -14566,7 +14567,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>1654</v>
       </c>
@@ -14577,7 +14578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>1656</v>
       </c>
@@ -14588,7 +14589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>1658</v>
       </c>
@@ -14599,7 +14600,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>1660</v>
       </c>
@@ -14610,7 +14611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>1662</v>
       </c>
@@ -14621,7 +14622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>1664</v>
       </c>
@@ -14632,7 +14633,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="828" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>1666</v>
       </c>
@@ -14643,7 +14644,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="829" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>1668</v>
       </c>
@@ -14654,7 +14655,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="830" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>1670</v>
       </c>
@@ -14665,7 +14666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="831" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>1672</v>
       </c>
@@ -14676,7 +14677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="832" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>1674</v>
       </c>
@@ -14687,7 +14688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="833" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>1676</v>
       </c>
@@ -14698,7 +14699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="834" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>1678</v>
       </c>
@@ -14709,7 +14710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="835" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>1680</v>
       </c>
@@ -14720,7 +14721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="836" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>1682</v>
       </c>
@@ -14731,7 +14732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="837" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>1684</v>
       </c>
@@ -14742,7 +14743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="838" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>1686</v>
       </c>
@@ -14753,7 +14754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="839" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>1688</v>
       </c>
@@ -14764,7 +14765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="840" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>1690</v>
       </c>
@@ -14775,7 +14776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="841" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>1692</v>
       </c>
@@ -14786,7 +14787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="842" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>1694</v>
       </c>
@@ -14797,7 +14798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="843" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>1696</v>
       </c>
@@ -14808,7 +14809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="844" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>1698</v>
       </c>
@@ -14819,7 +14820,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="845" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>1700</v>
       </c>
@@ -14830,7 +14831,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="846" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>1702</v>
       </c>
@@ -14841,7 +14842,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="847" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>1704</v>
       </c>
@@ -14852,7 +14853,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>1706</v>
       </c>
@@ -14863,7 +14864,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="849" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>1708</v>
       </c>
@@ -14874,7 +14875,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="850" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>1710</v>
       </c>
@@ -14885,7 +14886,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="851" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>1712</v>
       </c>
@@ -14897,7 +14898,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C851" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="C1:C851" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Diğer Şemsiye Fonu"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>